--- a/sim/rosenthal_output/melt_pool_dimensions_combined.xlsx
+++ b/sim/rosenthal_output/melt_pool_dimensions_combined.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Python\ME1573_data_processing\sim\rosenthal_output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ME1573_data_processing\sim\rosenthal_output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{D724C876-4D93-4D98-8BE2-D714AAF5926D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0147A8D1-8262-482B-85A5-FDE2509E2E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" activeTab="2" xr2:uid="{7CB7725D-D4DD-4D26-A040-A2E7AEF55077}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="3" activeTab="4" xr2:uid="{7CB7725D-D4DD-4D26-A040-A2E7AEF55077}"/>
   </bookViews>
   <sheets>
     <sheet name="250W" sheetId="5" r:id="rId1"/>
@@ -19,7 +19,20 @@
     <sheet name="500W" sheetId="3" r:id="rId4"/>
     <sheet name="combined results" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -649,6 +662,840 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'400W'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>length_mm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'400W'!$A$2:$A$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'400W'!$B$2:$B$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0.325814536340852</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.28571428571428498</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.26566416040100199</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.255639097744361</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.24561403508771901</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.23558897243107699</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.23057644110275599</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.22556390977443599</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.220551378446115</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.215538847117794</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.215538847117794</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.21052631578947301</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.21052631578947301</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.20551378446115201</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.20551378446115201</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.20551378446115201</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.20050125313283201</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.20050125313283201</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.20050125313283201</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.19548872180451099</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.19548872180451099</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E0A0-42BF-9C77-F2F34D9B9189}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'400W'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>width_mm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'400W'!$A$2:$A$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'400W'!$E$2:$E$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0.325814536340852</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.28571428571428498</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.255639097744361</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.23558897243107699</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.22556390977443599</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20551378446115201</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.19548872180451099</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.185463659147869</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.185463659147869</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.175438596491228</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.16541353383458601</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.16541353383458601</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.15538847117794399</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.15538847117794399</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.145363408521303</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.145363408521303</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.145363408521303</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.13533834586466101</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.13533834586466101</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.13533834586466101</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.12531328320801999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-E0A0-42BF-9C77-F2F34D9B9189}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'400W'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>depth_mm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'400W'!$A$2:$A$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'400W'!$F$2:$F$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0.16541353383458601</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.140350877192982</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.12531328320801999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.115288220551378</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.105263157894736</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.10025062656641601</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.0225563909774403E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.5213032581453602E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.02005012531328E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.02005012531328E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.5187969924811998E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.0175438596491196E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.0175438596491196E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.5162907268170395E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.5162907268170395E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6.01503759398496E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.01503759398496E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.5137844611528798E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.5137844611528798E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.5137844611528798E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.0125313283208003E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-E0A0-42BF-9C77-F2F34D9B9189}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="621562208"/>
+        <c:axId val="1532810256"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="621562208"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+          <c:max val="2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1532810256"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1532810256"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+          <c:max val="0.4"/>
+          <c:min val="4.0000000000000008E-2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="621562208"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
         <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -965,7 +1812,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1403,6 +2250,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2435,7 +3322,564 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>577850</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{082EDCC5-ABD4-A7D5-5046-984926478F7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2476,7 +3920,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2835,9 +4279,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29F74350-4F0A-4508-88C5-F6E158CBCA97}">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2857,7 +4301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2889,7 +4333,7 @@
         <v>1.2658224459701876E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>0.1</v>
       </c>
@@ -2921,7 +4365,7 @@
         <v>7.5912363578645614E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>0.2</v>
       </c>
@@ -2953,7 +4397,7 @@
         <v>7.8014654593179883E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>0.3</v>
       </c>
@@ -2985,7 +4429,7 @@
         <v>4.9751389206286509E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0.4</v>
       </c>
@@ -3017,7 +4461,7 @@
         <v>4.6776793299722889E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>0.5</v>
       </c>
@@ -3049,7 +4493,7 @@
         <v>3.2271058275436165E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>0.6</v>
       </c>
@@ -3081,7 +4525,7 @@
         <v>6.8408437183491849E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>0.7</v>
       </c>
@@ -3113,7 +4557,7 @@
         <v>4.0180144490105492E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>0.8</v>
       </c>
@@ -3145,7 +4589,7 @@
         <v>7.2772681001687762E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>0.9</v>
       </c>
@@ -3177,7 +4621,7 @@
         <v>2.9425928853692426E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1</v>
       </c>
@@ -3209,7 +4653,7 @@
         <v>2.7845104973816159E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1.1000000000000001</v>
       </c>
@@ -3241,7 +4685,7 @@
         <v>5.8828168023458218E-5</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1.2</v>
       </c>
@@ -3273,7 +4717,7 @@
         <v>2.6012706165983786E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1.3</v>
       </c>
@@ -3305,7 +4749,7 @@
         <v>5.1483761772716539E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1.4</v>
       </c>
@@ -3337,7 +4781,7 @@
         <v>2.6270869637345363E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1.5</v>
       </c>
@@ -3369,7 +4813,7 @@
         <v>2.5167240063183288E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1.6</v>
       </c>
@@ -3401,7 +4845,7 @@
         <v>1.9934775274443432E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1.7</v>
       </c>
@@ -3433,7 +4877,7 @@
         <v>8.3843872661049521E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1.8</v>
       </c>
@@ -3465,7 +4909,7 @@
         <v>6.0985583074464327E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1.9</v>
       </c>
@@ -3497,7 +4941,7 @@
         <v>3.9216435585054436E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2</v>
       </c>
@@ -3537,9 +4981,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B7BB8B4-AA71-42C8-9D0B-3A395C38B8FD}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3559,7 +5003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3594,7 +5038,7 @@
         <v>0.61352441800000002</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>0.1</v>
       </c>
@@ -3626,7 +5070,7 @@
         <v>8.1692733084137437E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>0.2</v>
       </c>
@@ -3658,7 +5102,7 @@
         <v>5.8599461722190355E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>0.3</v>
       </c>
@@ -3690,7 +5134,7 @@
         <v>4.0873333804112427E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0.4</v>
       </c>
@@ -3722,7 +5166,7 @@
         <v>4.3133455958210831E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>0.5</v>
       </c>
@@ -3754,7 +5198,7 @@
         <v>3.8173067018974632E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>0.6</v>
       </c>
@@ -3786,7 +5230,7 @@
         <v>2.800439580129703E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>0.7</v>
       </c>
@@ -3818,7 +5262,7 @@
         <v>1.3837987366581497E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>0.8</v>
       </c>
@@ -3850,7 +5294,7 @@
         <v>3.5281209573392175E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>0.9</v>
       </c>
@@ -3882,7 +5326,7 @@
         <v>1.2587903214121149E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1</v>
       </c>
@@ -3914,7 +5358,7 @@
         <v>9.2104041078799187E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1.1000000000000001</v>
       </c>
@@ -3946,7 +5390,7 @@
         <v>4.0005701952941508E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1.2</v>
       </c>
@@ -3978,7 +5422,7 @@
         <v>2.1067982780731756E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1.3</v>
       </c>
@@ -4010,7 +5454,7 @@
         <v>9.9817593838881502E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1.4</v>
       </c>
@@ -4042,7 +5486,7 @@
         <v>4.0224948507638913E-5</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1.5</v>
       </c>
@@ -4074,7 +5518,7 @@
         <v>2.8138290200168878E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1.6</v>
       </c>
@@ -4106,7 +5550,7 @@
         <v>1.921741304877024E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1.7</v>
       </c>
@@ -4138,7 +5582,7 @@
         <v>1.0778498261963601E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1.8</v>
       </c>
@@ -4170,7 +5614,7 @@
         <v>2.7749771731199607E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1.9</v>
       </c>
@@ -4202,7 +5646,7 @@
         <v>4.833105302182103E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4234,7 +5678,7 @@
         <v>2.7520300876948331E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="I23">
         <f>AVERAGE(I2:I22)</f>
         <v>2.2423206416332759E-3</v>
@@ -4248,9 +5692,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73AECF71-07EB-45F7-91E1-820AB0CD1E59}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4270,7 +5714,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4305,7 +5749,7 @@
         <v>0.71199999999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>0.1</v>
       </c>
@@ -4337,7 +5781,7 @@
         <v>1.00039901646512E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>0.2</v>
       </c>
@@ -4369,7 +5813,7 @@
         <v>7.401238465138793E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>0.3</v>
       </c>
@@ -4401,7 +5845,7 @@
         <v>7.4419941130574735E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0.4</v>
       </c>
@@ -4433,7 +5877,7 @@
         <v>5.6788289603373482E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>0.5</v>
       </c>
@@ -4465,7 +5909,7 @@
         <v>2.7356475449332729E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>0.6</v>
       </c>
@@ -4497,7 +5941,7 @@
         <v>2.5073392709716175E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>0.7</v>
       </c>
@@ -4529,7 +5973,7 @@
         <v>1.747119717819115E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>0.8</v>
       </c>
@@ -4561,7 +6005,7 @@
         <v>5.6521346534840755E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>0.9</v>
       </c>
@@ -4593,7 +6037,7 @@
         <v>9.614095221651478E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1</v>
       </c>
@@ -4625,7 +6069,7 @@
         <v>1.0063625487033434E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1.1000000000000001</v>
       </c>
@@ -4657,7 +6101,7 @@
         <v>1.012381765671283E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1.2</v>
       </c>
@@ -4689,7 +6133,7 @@
         <v>6.1683739887957723E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1.3</v>
       </c>
@@ -4721,7 +6165,7 @@
         <v>1.7701515286767597E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1.4</v>
       </c>
@@ -4753,7 +6197,7 @@
         <v>3.9304119211723554E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1.5</v>
       </c>
@@ -4785,7 +6229,7 @@
         <v>8.9629251978750463E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1.6</v>
       </c>
@@ -4817,7 +6261,7 @@
         <v>1.8866180073855293E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1.7</v>
       </c>
@@ -4849,7 +6293,7 @@
         <v>7.7307445945287018E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1.8</v>
       </c>
@@ -4881,7 +6325,7 @@
         <v>2.7903452164981801E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1.9</v>
       </c>
@@ -4913,7 +6357,7 @@
         <v>2.7977454842036051E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4945,7 +6389,7 @@
         <v>1.8755810214809016E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="I23">
         <f>AVERAGE(I2:I22)</f>
         <v>2.5525254525957529E-3</v>
@@ -4953,15 +6397,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A149ABB0-46DA-47A6-BBE9-2C08C5125F2B}">
   <dimension ref="A1:M23"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4981,7 +6426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5026,7 +6471,7 @@
         <v>6.2695550078049377E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>0.1</v>
       </c>
@@ -5068,7 +6513,7 @@
         <v>3.9429250464418485E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>0.2</v>
       </c>
@@ -5110,7 +6555,7 @@
         <v>2.5431034179019827E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>0.3</v>
       </c>
@@ -5152,7 +6597,7 @@
         <v>3.2019928168848626E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0.4</v>
       </c>
@@ -5194,7 +6639,7 @@
         <v>5.6492360309748756E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>0.5</v>
       </c>
@@ -5236,7 +6681,7 @@
         <v>2.9640712558490611E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>0.6</v>
       </c>
@@ -5278,7 +6723,7 @@
         <v>2.7256122117090107E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>0.7</v>
       </c>
@@ -5320,7 +6765,7 @@
         <v>2.4160215167896024E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>0.8</v>
       </c>
@@ -5362,7 +6807,7 @@
         <v>2.4644154263234442E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>0.9</v>
       </c>
@@ -5404,7 +6849,7 @@
         <v>2.4138647094080886E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1</v>
       </c>
@@ -5446,7 +6891,7 @@
         <v>2.3997903363253644E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1.1000000000000001</v>
       </c>
@@ -5488,7 +6933,7 @@
         <v>2.4037447000437198E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1.2</v>
       </c>
@@ -5524,7 +6969,7 @@
         <v>0.20500314476037973</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1.3</v>
       </c>
@@ -5560,7 +7005,7 @@
         <v>0.19767402190197578</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1.4</v>
       </c>
@@ -5596,7 +7041,7 @@
         <v>0.19086924860115179</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1.5</v>
       </c>
@@ -5632,7 +7077,7 @@
         <v>0.18452560744631347</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1.6</v>
       </c>
@@ -5668,7 +7113,7 @@
         <v>0.17859076928600515</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1.7</v>
       </c>
@@ -5704,7 +7149,7 @@
         <v>0.17302088865914136</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1.8</v>
       </c>
@@ -5740,7 +7185,7 @@
         <v>0.16777883642822466</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1.9</v>
       </c>
@@ -5776,7 +7221,7 @@
         <v>0.16283287539369717</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2</v>
       </c>
@@ -5812,7 +7257,7 @@
         <v>0.15815565084079197</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="I23">
         <f>AVERAGE(I2:I22)</f>
         <v>2.3997903363253644E-3</v>
@@ -5827,12 +7272,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC03A70D-B802-4B32-BFF4-6E483AA26D29}">
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="10" max="10" width="11.76171875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -5852,7 +7297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>300</v>
       </c>
@@ -5878,7 +7323,7 @@
         <v>0.35001164449243161</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>400</v>
       </c>
@@ -5904,7 +7349,7 @@
         <v>0.1794198700073506</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>500</v>
       </c>
@@ -5920,7 +7365,7 @@
         <v>0.6139</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D5">
         <v>350</v>
       </c>
@@ -5929,7 +7374,7 @@
         <v>0.66390000000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D6">
         <v>400</v>
       </c>
@@ -5938,7 +7383,7 @@
         <v>0.71389999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D7">
         <v>450</v>
       </c>
@@ -5947,7 +7392,7 @@
         <v>0.76390000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D8">
         <v>500</v>
       </c>
